--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\only_readmes\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FE6B85-4E10-4B97-98B8-A82238A3058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E433C7-F4C6-4CE6-B262-62647ECEA289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E2B4428-0ED6-4F07-9A40-88FCB22F6A60}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="17520" xr2:uid="{2E2B4428-0ED6-4F07-9A40-88FCB22F6A60}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="243">
   <si>
     <t>Category</t>
   </si>
@@ -628,6 +628,144 @@
   </si>
   <si>
     <t>https://youtu.be/GElkDW-AaiU</t>
+  </si>
+  <si>
+    <t>Microsoft Ai</t>
+  </si>
+  <si>
+    <t>Herramienta Gestion Ordenes asistida por Copilot</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HSUeJGwfG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introducción a Google ADK, Agent Development Kit </t>
+  </si>
+  <si>
+    <t>https://youtu.be/I3L1_r8SvIM</t>
+  </si>
+  <si>
+    <t>MCP Toolbox para BigQuery y Bases de Datos con ADK</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fBDQyn_8AEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis  Técnicas Avanzadas de Razonamiento con LLMs. CoT and React </t>
+  </si>
+  <si>
+    <t>Agentic IA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/H6qsnakYLeQ</t>
+  </si>
+  <si>
+    <t>Crear Grafico de Conocimientos con  Google ADK y Neo4J</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MMBQdksQlJI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZKjTdAzlgts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSSQL MCP Server con OAuth 2.0 e Integración ChatGPT </t>
+  </si>
+  <si>
+    <t>https://youtu.be/0yNpz3AdpU8</t>
+  </si>
+  <si>
+    <t>Agentic Workflows</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HYKo53KGGYU</t>
+  </si>
+  <si>
+    <t>Como usar OpenaAPI tools en  Google ADK agents</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UW-iBRC7Vnw</t>
+  </si>
+  <si>
+    <t>Conectar Azure Ai Foundry agents con OpenAPI tools</t>
+  </si>
+  <si>
+    <t>https://youtu.be/n1Mm9fZadGc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conecte datos privados con OpenAPI a custos GPT con acciones en ChatGPT </t>
+  </si>
+  <si>
+    <t>OpenApi / ChatGPT</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ISaWVITPkZc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6DwHnDNIA8c</t>
+  </si>
+  <si>
+    <t>Copilot Assisted Order Management Tool</t>
+  </si>
+  <si>
+    <t>https://youtu.be/G88myIILLS4</t>
+  </si>
+  <si>
+    <t>Introduction to Google ADK, Agent Development Kit</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eZycQQa7WoM</t>
+  </si>
+  <si>
+    <t>MCP Toolbox for BigQuery and Databases with ADK</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FsEWxmN8Md4</t>
+  </si>
+  <si>
+    <t>Agentic AI</t>
+  </si>
+  <si>
+    <t>Deep Dive Advanced Reasoning Techniques with LLMs. CoT and React</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Vn_vKkn0dZA</t>
+  </si>
+  <si>
+    <t>Build a Knowledge Graph with Google ADK and Neo4J</t>
+  </si>
+  <si>
+    <t>https://youtu.be/n64r9_Y6ZoI</t>
+  </si>
+  <si>
+    <t>MSSQL MCP Server with OAuth 2.0 and ChatGPT Integration</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GQMwCczHQQ8</t>
+  </si>
+  <si>
+    <t>How to Agentic Workflows</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uvLA5d0sx6s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Jfk3uBA_ZCc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connect private data with OpenAPI to custom GPTs using actions in ChatGPT </t>
+  </si>
+  <si>
+    <t>https://youtu.be/2ZQqWyhp8ew</t>
+  </si>
+  <si>
+    <t>How to use OpenAPI tools with Google ADK agents</t>
+  </si>
+  <si>
+    <t>Connect Azure Ai Foundry agents with OpenAPI tools</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DnC3wfTQxg0</t>
   </si>
 </sst>
 </file>
@@ -1010,12 +1148,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D99564-D1DD-43A9-84D6-3D9D11EE9895}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="65.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1280,6 +1418,9 @@
       <c r="C19" t="s">
         <v>126</v>
       </c>
+      <c r="D19" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1402,21 +1543,135 @@
       </c>
       <c r="D28" s="1" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>226</v>
+      </c>
+      <c r="D31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D27" r:id="rId1" xr:uid="{A180A2C2-23D6-417F-A8B8-5828452C276E}"/>
     <hyperlink ref="D28" r:id="rId2" xr:uid="{0579DA10-CA28-4189-BD17-60EFC81902C6}"/>
+    <hyperlink ref="D29" r:id="rId3" xr:uid="{C114272C-92E0-417E-B9F4-D0FE7723B80E}"/>
+    <hyperlink ref="D34" r:id="rId4" xr:uid="{8B0A1943-CDC6-43AD-92B6-E9005CFEBC27}"/>
+    <hyperlink ref="D35" r:id="rId5" xr:uid="{21D1C31E-30DD-46D7-90C1-78B405EAB7AA}"/>
+    <hyperlink ref="D30" r:id="rId6" xr:uid="{36241D4F-F576-4368-9243-63D1E29C0A58}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DDC66B-0FDD-4074-BCC5-74B5022F1D6B}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
@@ -1686,6 +1941,9 @@
       <c r="C19" t="s">
         <v>107</v>
       </c>
+      <c r="D19" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1822,6 +2080,116 @@
       </c>
       <c r="D29" s="1" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" t="s">
+        <v>218</v>
+      </c>
+      <c r="D39" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -1829,8 +2197,9 @@
     <hyperlink ref="D20" r:id="rId1" xr:uid="{F50146AA-8EAF-4FE3-AFA6-9AE79227D3BF}"/>
     <hyperlink ref="D15" r:id="rId2" xr:uid="{5F1533BD-C5AB-415E-8F29-3C1F624650B8}"/>
     <hyperlink ref="D29" r:id="rId3" xr:uid="{C139E005-9140-49BE-A695-AB9E451C1336}"/>
+    <hyperlink ref="D30" r:id="rId4" xr:uid="{5F17ACCF-380D-46A1-969F-2716063792D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>